--- a/Deshe_LayerMaker/configuration/domains.xlsx
+++ b/Deshe_LayerMaker/configuration/domains.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tauex-my.sharepoint.com/personal/yoskoyoav_tauex_tau_ac_il/Documents/Development/מכון דשא ואחר/כלי ליצירת שכבות/כלי ליצירת שכבות/DesheTools/configuration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galisraeli\Documents\GitHub\my-project\Deshe_LayerMaker\configuration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_F25DC773A252ABDACC10483551DE74305BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFDCBCA1-8C0C-4567-9193-A4AB0BBB88CF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E04F42-8B89-42D7-B594-AE7EF9B6F5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>domain_name</t>
   </si>
@@ -93,10 +93,40 @@
     <t>עמית מנדלסון</t>
   </si>
   <si>
-    <t>INBAR_S</t>
-  </si>
-  <si>
-    <t>ענבר שניצר</t>
+    <t>URI_W</t>
+  </si>
+  <si>
+    <t>אורי וולקובסקי</t>
+  </si>
+  <si>
+    <t>נוי שפירא</t>
+  </si>
+  <si>
+    <t>NOY_S</t>
+  </si>
+  <si>
+    <t>אחר</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>LIRAZ_C</t>
+  </si>
+  <si>
+    <t>לירז כברה</t>
+  </si>
+  <si>
+    <t>איתן רומם</t>
+  </si>
+  <si>
+    <t>EITAN_R</t>
+  </si>
+  <si>
+    <t>יוני אלירז</t>
+  </si>
+  <si>
+    <t>YONI_E</t>
   </si>
 </sst>
 </file>
@@ -423,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -552,6 +582,61 @@
         <v>23</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
